--- a/Kit-Coleta-Dados-Carbono.xlsx
+++ b/Kit-Coleta-Dados-Carbono.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Fixação - Remoções" sheetId="6" r:id="rId6"/>
     <sheet name="Checklist" sheetId="7" r:id="rId7"/>
   </sheets>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -106,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -136,6 +137,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumFmt="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumFmt="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -145,9 +152,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <cols>
-    <col min="1" max="1" width="92" customWidth="1"/>
+    <col min="1" max="1" width="96" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -160,7 +167,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preencha esta planilha com os dados da sua operação no período. Com ela, a Carbona calcula suas emissões (escopos 1, 2 e 3) e a fixação de carbono. Esta planilha NÃO é o protocolo — é o formulário de dados que alimenta o cálculo.</t>
+          <t xml:space="preserve">Formulário de DADOS que a Carbona usa para calcular suas emissões e a fixação de carbono. NÃO é o protocolo.</t>
         </is>
       </c>
     </row>
@@ -175,82 +182,89 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Informe o período de referência e os dados gerais na aba "Dados da Empresa".</t>
+          <t xml:space="preserve">1. Preencha a aba "Dados da Empresa".</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Preencha os consumos nas abas "Escopo 1", "Escopo 2" e "Escopo 3". As células em AMARELO são para você preencher.</t>
+          <t xml:space="preserve">2. Em cada aba de Escopo, informe o consumo MÊS A MÊS (colunas Jan a Dez). A coluna "Total (ano)" é calculada sozinha.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. Registre as áreas de vegetação e solo na aba "Fixação - Remoções" (área e manejo; os fatores são aplicados pela Carbona).</t>
+          <t xml:space="preserve">3. As células em AMARELO são para preencher. Não sabe um mês? Deixe em branco.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">4. Confira a aba "Checklist" e separe os documentos comprobatórios (notas, contas, contratos).</t>
+          <t xml:space="preserve">4. Para enviar VÁRIOS ANOS, salve uma cópia do arquivo por ano (ex.: Kit-2024.xlsx, Kit-2025.xlsx) e informe o ano no topo de cada aba.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5. Envie a planilha preenchida para contato@carbona.com.br. Devolvemos o relatório em tCO₂e por escopo e por fonte, com o balanço de carbono.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Legenda e dicas</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">5. Na aba "Fixação", informe as áreas (ha) e o ano/período de cada uma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6. Confira o "Checklist" e envie a planilha para contato@carbona.com.br. Devolvemos o relatório em tCO₂e.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">• Células em AMARELO = para você preencher.</t>
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legenda</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">• Não sabe algum dado? Deixe em branco e escreva na coluna "Observações" — ajudamos a estimar.</t>
+          <t xml:space="preserve">• Células AMARELAS = para você preencher.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">• Use ponto ou vírgula para decimais; informe sempre a unidade pedida.</t>
+          <t xml:space="preserve">• Coluna "Total (ano)" = calculada automaticamente (soma de Jan a Dez).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">• Prazo promocional: as primeiras cotações são devolvidas em menos de 24 horas.</t>
+          <t xml:space="preserve">• Prefere preencher na web? Use o Kit de Coleta online no site — lá dá para enviar vários meses/anos direto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Promoção: as primeiras cotações são devolvidas em menos de 24 horas.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
+  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B17"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="46" customWidth="1"/>
@@ -266,7 +280,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preencha os campos destacados em amarelo.</t>
+          <t xml:space="preserve">Preencha os campos destacados em amarelo. Valem para todos os períodos.</t>
         </is>
       </c>
     </row>
@@ -314,7 +328,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ano-base do inventário</t>
+          <t xml:space="preserve">Ano-base / anos do inventário</t>
         </is>
       </c>
       <c r="B9" s="9"/>
@@ -322,7 +336,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Período de referência — início (mês/ano)</t>
+          <t xml:space="preserve">Nº de unidades / plantas</t>
         </is>
       </c>
       <c r="B10" s="9"/>
@@ -330,7 +344,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Período de referência — fim (mês/ano)</t>
+          <t xml:space="preserve">Nº de funcionários</t>
         </is>
       </c>
       <c r="B11" s="9"/>
@@ -338,7 +352,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nº de unidades / plantas</t>
+          <t xml:space="preserve">Faturamento anual (R$)</t>
         </is>
       </c>
       <c r="B12" s="9"/>
@@ -346,7 +360,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nº de funcionários</t>
+          <t xml:space="preserve">Unidade de produto (ex.: t, un, m³)</t>
         </is>
       </c>
       <c r="B13" s="9"/>
@@ -354,7 +368,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Faturamento anual (R$)</t>
+          <t xml:space="preserve">Produção no período (para intensidade)</t>
         </is>
       </c>
       <c r="B14" s="9"/>
@@ -362,7 +376,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidade de produto (ex.: t, un, m³)</t>
+          <t xml:space="preserve">Responsável pelo preenchimento</t>
         </is>
       </c>
       <c r="B15" s="9"/>
@@ -370,7 +384,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Produção no período (para intensidade)</t>
+          <t xml:space="preserve">E-mail</t>
         </is>
       </c>
       <c r="B16" s="9"/>
@@ -378,224 +392,379 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Responsável pelo preenchimento</t>
+          <t xml:space="preserve">Telefone / WhatsApp</t>
         </is>
       </c>
       <c r="B17" s="9"/>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">E-mail</t>
-        </is>
-      </c>
-      <c r="B18" s="9"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Telefone</t>
-        </is>
-      </c>
-      <c r="B19" s="9"/>
-    </row>
   </sheetData>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
+  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:P15"/>
   <cols>
-    <col min="1" max="1" width="46" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="6" customWidth="1"/>
+    <col min="4" max="4" width="6" customWidth="1"/>
+    <col min="5" max="5" width="6" customWidth="1"/>
+    <col min="6" max="6" width="6" customWidth="1"/>
+    <col min="7" max="7" width="6" customWidth="1"/>
+    <col min="8" max="8" width="6" customWidth="1"/>
+    <col min="9" max="9" width="6" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="6" customWidth="1"/>
+    <col min="13" max="13" width="6" customWidth="1"/>
+    <col min="14" max="14" width="6" customWidth="1"/>
+    <col min="15" max="15" width="12" customWidth="1"/>
+    <col min="16" max="16" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Escopo 1 — Emissões Diretas</t>
+          <t xml:space="preserve">Escopo 1 — Emissões Diretas (mês a mês)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Combustíveis queimados na sua operação e gases. Informe o total consumido no período.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+          <t xml:space="preserve">Combustíveis queimados na operação e gases. Informe o consumo de cada mês.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ano de referência:</t>
+        </is>
+      </c>
+      <c r="B3" s="9"/>
+    </row>
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Fonte</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidade</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consumo no período</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Período (mês/ano ou ano)</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jan</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fev</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mar</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abr</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mai</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jun</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jul</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ago</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Set</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Out</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nov</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dez</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total (ano)</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Observações</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Diesel</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">litros (L)</t>
-        </is>
-      </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasolina</t>
+          <t xml:space="preserve">Diesel</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">litros (L)</t>
-        </is>
-      </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
+          <t xml:space="preserve">L</t>
+        </is>
+      </c>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="12">
+        <f>SUM(C6:N6)</f>
+        <v>0</v>
+      </c>
+      <c r="P6" s="9"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Etanol (hidratado)</t>
+          <t xml:space="preserve">Gasolina</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">litros (L)</t>
-        </is>
-      </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
+          <t xml:space="preserve">L</t>
+        </is>
+      </c>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="12">
+        <f>SUM(C7:N7)</f>
+        <v>0</v>
+      </c>
+      <c r="P7" s="9"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">GLP</t>
+          <t xml:space="preserve">Etanol (hidratado)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">kg</t>
-        </is>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
+          <t xml:space="preserve">L</t>
+        </is>
+      </c>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="12">
+        <f>SUM(C8:N8)</f>
+        <v>0</v>
+      </c>
+      <c r="P8" s="9"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gás natural</t>
+          <t xml:space="preserve">GLP</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">m³</t>
-        </is>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
+          <t xml:space="preserve">kg</t>
+        </is>
+      </c>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="12">
+        <f>SUM(C9:N9)</f>
+        <v>0</v>
+      </c>
+      <c r="P9" s="9"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Óleo diesel de geradores</t>
+          <t xml:space="preserve">Gás natural</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">litros (L)</t>
-        </is>
-      </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
+          <t xml:space="preserve">m³</t>
+        </is>
+      </c>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="12">
+        <f>SUM(C10:N10)</f>
+        <v>0</v>
+      </c>
+      <c r="P10" s="9"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lenha / biomassa</t>
+          <t xml:space="preserve">Óleo diesel de geradores</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">toneladas (t)</t>
-        </is>
-      </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
+          <t xml:space="preserve">L</t>
+        </is>
+      </c>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="12">
+        <f>SUM(C11:N11)</f>
+        <v>0</v>
+      </c>
+      <c r="P11" s="9"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gases refrigerantes — recarga (informe o tipo em obs.)</t>
+          <t xml:space="preserve">Lenha / biomassa</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">kg</t>
-        </is>
-      </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
+          <t xml:space="preserve">t</t>
+        </is>
+      </c>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="12">
+        <f>SUM(C12:N12)</f>
+        <v>0</v>
+      </c>
+      <c r="P12" s="9"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outro (especifique em observações)</t>
+          <t xml:space="preserve">Gases refrigerantes — recarga (tipo em Observações)</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
+          <t xml:space="preserve">kg</t>
+        </is>
+      </c>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="12">
+        <f>SUM(C13:N13)</f>
+        <v>0</v>
+      </c>
+      <c r="P13" s="9"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outro (especifique em observações)</t>
+          <t xml:space="preserve">Outro (especifique em Observações)</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -603,87 +772,189 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="12">
+        <f>SUM(C14:N14)</f>
+        <v>0</v>
+      </c>
+      <c r="P14" s="9"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outro (especifique em Observações)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="12">
+        <f>SUM(C15:N15)</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="9"/>
     </row>
   </sheetData>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
+  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:P10"/>
   <cols>
-    <col min="1" max="1" width="44" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="6" customWidth="1"/>
+    <col min="4" max="4" width="6" customWidth="1"/>
+    <col min="5" max="5" width="6" customWidth="1"/>
+    <col min="6" max="6" width="6" customWidth="1"/>
+    <col min="7" max="7" width="6" customWidth="1"/>
+    <col min="8" max="8" width="6" customWidth="1"/>
+    <col min="9" max="9" width="6" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="6" customWidth="1"/>
+    <col min="13" max="13" width="6" customWidth="1"/>
+    <col min="14" max="14" width="6" customWidth="1"/>
+    <col min="15" max="15" width="12" customWidth="1"/>
+    <col min="16" max="16" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Escopo 2 — Energia</t>
+          <t xml:space="preserve">Escopo 2 — Energia (mês a mês)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energia adquirida de terceiros (comprada).</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Item</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+          <t xml:space="preserve">Energia adquirida de terceiros. Informe o consumo de cada mês.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ano de referência:</t>
+        </is>
+      </c>
+      <c r="B3" s="9"/>
+    </row>
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fonte</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidade</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consumo no período</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unidade / planta</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jan</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fev</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mar</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abr</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mai</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jun</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jul</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ago</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Set</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Out</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nov</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dez</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total (ano)</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Observações</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Energia elétrica adquirida (rede)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kWh</t>
-        </is>
-      </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energia elétrica — outra unidade</t>
+          <t xml:space="preserve">Energia elétrica adquirida (rede)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -691,14 +962,28 @@
           <t xml:space="preserve">kWh</t>
         </is>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="12">
+        <f>SUM(C6:N6)</f>
+        <v>0</v>
+      </c>
+      <c r="P6" s="9"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energia renovável certificada (I-REC / PPA)</t>
+          <t xml:space="preserve">Energia elétrica — outra unidade</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -706,162 +991,334 @@
           <t xml:space="preserve">kWh</t>
         </is>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="12">
+        <f>SUM(C7:N7)</f>
+        <v>0</v>
+      </c>
+      <c r="P7" s="9"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vapor / calor / frio adquirido</t>
+          <t xml:space="preserve">Energia renovável (I-REC / PPA)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">kWh ou GJ</t>
-        </is>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
+          <t xml:space="preserve">kWh</t>
+        </is>
+      </c>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="12">
+        <f>SUM(C8:N8)</f>
+        <v>0</v>
+      </c>
+      <c r="P8" s="9"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outro (especifique em observações)</t>
+          <t xml:space="preserve">Vapor / calor / frio adquirido</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">kWh/GJ</t>
+        </is>
+      </c>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="12">
+        <f>SUM(C9:N9)</f>
+        <v>0</v>
+      </c>
+      <c r="P9" s="9"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outro (especifique em Observações)</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="12">
+        <f>SUM(C10:N10)</f>
+        <v>0</v>
+      </c>
+      <c r="P10" s="9"/>
     </row>
   </sheetData>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
+  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:P15"/>
   <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="34" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="6" customWidth="1"/>
+    <col min="4" max="4" width="6" customWidth="1"/>
+    <col min="5" max="5" width="6" customWidth="1"/>
+    <col min="6" max="6" width="6" customWidth="1"/>
+    <col min="7" max="7" width="6" customWidth="1"/>
+    <col min="8" max="8" width="6" customWidth="1"/>
+    <col min="9" max="9" width="6" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="6" customWidth="1"/>
+    <col min="13" max="13" width="6" customWidth="1"/>
+    <col min="14" max="14" width="6" customWidth="1"/>
+    <col min="15" max="15" width="12" customWidth="1"/>
+    <col min="16" max="16" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Escopo 3 — Emissões Indiretas</t>
+          <t xml:space="preserve">Escopo 3 — Emissões Indiretas (mês a mês)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cadeia de valor: resíduos, transporte, viagens e deslocamentos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Categoria</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unidade sugerida</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Quantidade no período</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Detalhe (origem/destino, tipo)</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+          <t xml:space="preserve">Cadeia de valor: resíduos, transporte, viagens e deslocamentos. Informe cada mês.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ano de referência:</t>
+        </is>
+      </c>
+      <c r="B3" s="9"/>
+    </row>
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fonte</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jan</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fev</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mar</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abr</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mai</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jun</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jul</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ago</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Set</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Out</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nov</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dez</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total (ano)</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Observações</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Resíduos enviados a aterro</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">toneladas (t)</t>
-        </is>
-      </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resíduos reciclados / compostados</t>
+          <t xml:space="preserve">Resíduos enviados a aterro</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">toneladas (t)</t>
-        </is>
-      </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
+          <t xml:space="preserve">t</t>
+        </is>
+      </c>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="12">
+        <f>SUM(C6:N6)</f>
+        <v>0</v>
+      </c>
+      <c r="P6" s="9"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Efluentes tratados</t>
+          <t xml:space="preserve">Resíduos reciclados / compostados</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">m³</t>
-        </is>
-      </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
+          <t xml:space="preserve">t</t>
+        </is>
+      </c>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="12">
+        <f>SUM(C7:N7)</f>
+        <v>0</v>
+      </c>
+      <c r="P7" s="9"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fretes rodoviários (contratados)</t>
+          <t xml:space="preserve">Efluentes tratados</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">t.km (ou km + carga)</t>
-        </is>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
+          <t xml:space="preserve">m³</t>
+        </is>
+      </c>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="12">
+        <f>SUM(C8:N8)</f>
+        <v>0</v>
+      </c>
+      <c r="P8" s="9"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transporte de cargas — outros modais</t>
+          <t xml:space="preserve">Fretes rodoviários (contratados)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -869,29 +1326,57 @@
           <t xml:space="preserve">t.km</t>
         </is>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="12">
+        <f>SUM(C9:N9)</f>
+        <v>0</v>
+      </c>
+      <c r="P9" s="9"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viagens aéreas a negócios</t>
+          <t xml:space="preserve">Transporte — outros modais</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">km (ou trechos)</t>
-        </is>
-      </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
+          <t xml:space="preserve">t.km</t>
+        </is>
+      </c>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="12">
+        <f>SUM(C10:N10)</f>
+        <v>0</v>
+      </c>
+      <c r="P10" s="9"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viagens rodoviárias a negócios</t>
+          <t xml:space="preserve">Viagens aéreas a negócios</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -899,59 +1384,115 @@
           <t xml:space="preserve">km</t>
         </is>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="12">
+        <f>SUM(C11:N11)</f>
+        <v>0</v>
+      </c>
+      <c r="P11" s="9"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deslocamento casa-trabalho (funcionários)</t>
+          <t xml:space="preserve">Viagens rodoviárias a negócios</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">km/dia • nº pessoas</t>
-        </is>
-      </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
+          <t xml:space="preserve">km</t>
+        </is>
+      </c>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="12">
+        <f>SUM(C12:N12)</f>
+        <v>0</v>
+      </c>
+      <c r="P12" s="9"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Água consumida</t>
+          <t xml:space="preserve">Deslocamento casa-trabalho (equipe)</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">m³</t>
-        </is>
-      </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
+          <t xml:space="preserve">km</t>
+        </is>
+      </c>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="12">
+        <f>SUM(C13:N13)</f>
+        <v>0</v>
+      </c>
+      <c r="P13" s="9"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Compras / serviços relevantes</t>
+          <t xml:space="preserve">Água consumida</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
+          <t xml:space="preserve">m³</t>
+        </is>
+      </c>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="12">
+        <f>SUM(C14:N14)</f>
+        <v>0</v>
+      </c>
+      <c r="P14" s="9"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outro (especifique em observações)</t>
+          <t xml:space="preserve">Outro (especifique em Observações)</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -959,12 +1500,26 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="12">
+        <f>SUM(C15:N15)</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="9"/>
     </row>
   </sheetData>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
+  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -973,11 +1528,11 @@
   <dimension ref="A1:F12"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -990,12 +1545,12 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Áreas que removem e armazenam carbono (biomassa e solo). Informe a área e o manejo; os fatores de fixação são aplicados pela Carbona.</t>
+          <t xml:space="preserve">Áreas que removem e armazenam carbono. Informe a área (ha) e o ano/período. Para vários anos, use uma linha por ano. Os fatores são aplicados pela Carbona.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="26" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Categoria de fixação</t>
@@ -1003,22 +1558,22 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ano / período</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Área (ha)</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Espécie / idade / composição</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Práticas de manejo</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ano de início</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -1034,7 +1589,7 @@
         </is>
       </c>
       <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
+      <c r="C5" s="11"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
@@ -1046,7 +1601,7 @@
         </is>
       </c>
       <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
+      <c r="C6" s="11"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
@@ -1058,7 +1613,7 @@
         </is>
       </c>
       <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
+      <c r="C7" s="11"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -1070,7 +1625,7 @@
         </is>
       </c>
       <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
+      <c r="C8" s="11"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
@@ -1082,7 +1637,7 @@
         </is>
       </c>
       <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
+      <c r="C9" s="11"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
@@ -1094,7 +1649,7 @@
         </is>
       </c>
       <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
+      <c r="C10" s="11"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
@@ -1102,11 +1657,11 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outro (especifique em observações)</t>
+          <t xml:space="preserve">Outro (especifique em Observações)</t>
         </is>
       </c>
       <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
+      <c r="C11" s="11"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
@@ -1114,17 +1669,17 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outro (especifique em observações)</t>
+          <t xml:space="preserve">Outro (especifique em Observações)</t>
         </is>
       </c>
       <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
+      <c r="C12" s="11"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
     </row>
   </sheetData>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
+  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1152,7 +1707,7 @@
       </c>
     </row>
     <row r="3"/>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="26" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Documento</t>
@@ -1172,7 +1727,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notas fiscais de combustíveis</t>
+          <t xml:space="preserve">Notas fiscais de combustíveis (por mês)</t>
         </is>
       </c>
       <c r="B5" s="9"/>
@@ -1251,6 +1806,6 @@
       <c r="C13" s="9"/>
     </row>
   </sheetData>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
+  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
 </file>